--- a/assets/oracle-model.xlsx
+++ b/assets/oracle-model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/howard/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C348CC-A32A-674C-9009-0D6B0ED1876C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7FC28F-04D9-9443-8E53-BE0DCB6209D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17380" activeTab="5" xr2:uid="{1CB6DB0A-2E13-9B4A-BF39-0F22AC44DBF3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17380" activeTab="1" xr2:uid="{1CB6DB0A-2E13-9B4A-BF39-0F22AC44DBF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -60,668 +60,671 @@
 Institute of Science Tokyo</t>
   </si>
   <si>
+    <t>FY 2022</t>
+  </si>
+  <si>
+    <t>FY 2023</t>
+  </si>
+  <si>
+    <t>FY 2024</t>
+  </si>
+  <si>
+    <t>FY 2025</t>
+  </si>
+  <si>
+    <t>FY 2026</t>
+  </si>
+  <si>
+    <t>Income Statement</t>
+  </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
+  <si>
+    <t>Cloud Services &amp; License Support</t>
+  </si>
+  <si>
+    <t>Cloud License &amp; On- Premise License</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Cloud/Software Operating Expense</t>
+  </si>
+  <si>
+    <t>Hardware Operating Expense</t>
+  </si>
+  <si>
+    <t>Services Operating Expense</t>
+  </si>
+  <si>
+    <t>Sales &amp; Marketing</t>
+  </si>
+  <si>
+    <t>R &amp; D</t>
+  </si>
+  <si>
+    <t>G &amp; A</t>
+  </si>
+  <si>
+    <t>Amortization of Intangibles</t>
+  </si>
+  <si>
+    <t>Acquistion/Restructuring/Other</t>
+  </si>
+  <si>
+    <t>Total Operating Expense</t>
+  </si>
+  <si>
+    <t>Operating Income/EBIT</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Non-operating Income/Expense</t>
+  </si>
+  <si>
+    <t>Income Before Tax</t>
+  </si>
+  <si>
+    <t>Tax Provision</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Preferred Dividends</t>
+  </si>
+  <si>
+    <t>Net Income to Common</t>
+  </si>
+  <si>
+    <t>Basic EPS</t>
+  </si>
+  <si>
+    <t>Diluted EPS</t>
+  </si>
+  <si>
+    <t>Basic Shares</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>USD millions</t>
+  </si>
+  <si>
+    <t>Diluted Shares</t>
+  </si>
+  <si>
+    <t>Balance Sheet</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>Cash and Cash Equivalents</t>
+  </si>
+  <si>
+    <t>Maketable Securities</t>
+  </si>
+  <si>
+    <t>Trade Receivables,net</t>
+  </si>
+  <si>
+    <t>Prepaid Expenses and Other Current Assets</t>
+  </si>
+  <si>
+    <t>Total Current Assets</t>
+  </si>
+  <si>
+    <t>PP&amp;E,net</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>Operating Lease right-of-use Assets</t>
+  </si>
+  <si>
+    <t>Deferred Tax Assets</t>
+  </si>
+  <si>
+    <t>Other Non-Current Assets</t>
+  </si>
+  <si>
+    <t>Total Non-Current Assets</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>Liabilities</t>
+  </si>
+  <si>
+    <t>Notes Payable and Other Borrowings, Current</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>Accrued Compensation and Related Benefits</t>
+  </si>
+  <si>
+    <t>Deferred Revenues</t>
+  </si>
+  <si>
+    <t>Other Current Liabilites</t>
+  </si>
+  <si>
+    <t>Total Current Liabilities</t>
+  </si>
+  <si>
+    <t>Notes Payable and Other Borrowings, Non-Current</t>
+  </si>
+  <si>
+    <t>Income Taxes Payable</t>
+  </si>
+  <si>
+    <t>Operating Lease Liabilities</t>
+  </si>
+  <si>
+    <t>Other Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Total Liabilities</t>
+  </si>
+  <si>
+    <t>Total Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Stockholders' Equity</t>
+  </si>
+  <si>
+    <t>Balance Sheet Check</t>
+  </si>
+  <si>
+    <t>Red : Wrong</t>
+  </si>
+  <si>
+    <t>Yellow : Right</t>
+  </si>
+  <si>
+    <t>Cash Flow Statement</t>
+  </si>
+  <si>
+    <t>Operating Activities</t>
+  </si>
+  <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
+    <t>Deferred Income Taxes</t>
+  </si>
+  <si>
+    <t>Stock-Based Compensation/SBC</t>
+  </si>
+  <si>
+    <t>Other, net</t>
+  </si>
+  <si>
+    <t>Increase in Trade Receivables</t>
+  </si>
+  <si>
+    <t>Decrease in Prepaid &amp; Other Assets</t>
+  </si>
+  <si>
+    <t>Decrease in Income Taxes Payable</t>
+  </si>
+  <si>
+    <t>Decrease in AP &amp; Other Liabilities</t>
+  </si>
+  <si>
+    <t>Increase in Deferred Revenues</t>
+  </si>
+  <si>
+    <t>Customer Prepayments w/Significant Financing</t>
+  </si>
+  <si>
+    <t>Net Cash Provided by Operating Activities (OCF)</t>
+  </si>
+  <si>
+    <t>Investing Activities</t>
+  </si>
+  <si>
+    <t>Purchases of Marketable Securities &amp; Investments</t>
+  </si>
+  <si>
+    <t>Acquisition, Net of Cash Acquired</t>
+  </si>
+  <si>
+    <t>CapEx</t>
+  </si>
+  <si>
+    <t>Proceeds from Sales/Maturities of Investments</t>
+  </si>
+  <si>
+    <t>Net Cash Used/ Provided by Investing Activities</t>
+  </si>
+  <si>
+    <t>Financing Activities</t>
+  </si>
+  <si>
+    <t>Repurchase of Common Stock</t>
+  </si>
+  <si>
+    <t>Proceeds from Issurance of Common Stock</t>
+  </si>
+  <si>
+    <t>Tax Withholding on RSU Vesting RSU</t>
+  </si>
+  <si>
+    <t>Dividends Paid to Stockholders</t>
+  </si>
+  <si>
+    <t>Commercial Paper, Net</t>
+  </si>
+  <si>
+    <t>MCPS Issurance, Net</t>
+  </si>
+  <si>
+    <t>Short-Term Financing Activities, Net</t>
+  </si>
+  <si>
+    <t>Debt Issurance</t>
+  </si>
+  <si>
+    <t>Debt Repayment</t>
+  </si>
+  <si>
+    <t>Other Financing Activities,Net</t>
+  </si>
+  <si>
+    <t>Net Cash Provided/ Used by Financing Activities</t>
+  </si>
+  <si>
+    <t>FX Effect</t>
+  </si>
+  <si>
+    <t>Net Increase/ Decrease in Cash</t>
+  </si>
+  <si>
+    <t>Beginning Cash</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>FCF</t>
+  </si>
+  <si>
+    <t>EBIT Margin</t>
+  </si>
+  <si>
+    <t>CapEx Margin</t>
+  </si>
+  <si>
+    <t>FY 2025A</t>
+  </si>
+  <si>
+    <t>FY 2024A</t>
+  </si>
+  <si>
+    <t>FY 2023A</t>
+  </si>
+  <si>
+    <t>FY 2022A</t>
+  </si>
+  <si>
+    <t>FY 2026A</t>
+  </si>
+  <si>
+    <t>FY 2027E</t>
+  </si>
+  <si>
+    <t>FY 2028E</t>
+  </si>
+  <si>
+    <t>FY 2029E</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>D&amp;A Margin</t>
+  </si>
+  <si>
+    <t>Forecast Sheet</t>
+  </si>
+  <si>
+    <t>FY2027E</t>
+  </si>
+  <si>
+    <t>FY2028E</t>
+  </si>
+  <si>
+    <t>FY2029E</t>
+  </si>
+  <si>
+    <t>FY2026A</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>OCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Expense </t>
+  </si>
+  <si>
+    <t>SBC Margin</t>
+  </si>
+  <si>
+    <t>Deferred Taxes M</t>
+  </si>
+  <si>
+    <t>ΔNWC</t>
+  </si>
+  <si>
+    <t>FY 2030E</t>
+  </si>
+  <si>
+    <t>FY 2031E</t>
+  </si>
+  <si>
+    <t>FY 2032E</t>
+  </si>
+  <si>
+    <t>WACC Calculation</t>
+  </si>
+  <si>
+    <t>Risk-Free Rate</t>
+  </si>
+  <si>
+    <t>Equity Risk Premium</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Pre-tax Cost of Debt</t>
+  </si>
+  <si>
+    <t>After-tax Cost of Debt</t>
+  </si>
+  <si>
+    <t>Equity Weight</t>
+  </si>
+  <si>
+    <t>Debt Weight</t>
+  </si>
+  <si>
+    <t>WACC</t>
+  </si>
+  <si>
+    <t>Terminal Growth Rate</t>
+  </si>
+  <si>
+    <t>Terminal Value</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>Equity Value</t>
+  </si>
+  <si>
+    <t>Net Debt</t>
+  </si>
+  <si>
+    <t>Preferred  Equity</t>
+  </si>
+  <si>
+    <t>Present Target Price</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>P/E</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Bull Case</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Bear Case</t>
+  </si>
+  <si>
+    <t>Bull</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Bear</t>
+  </si>
+  <si>
+    <t>DCF Present Target Price</t>
+  </si>
+  <si>
+    <t>Present Value</t>
+  </si>
+  <si>
+    <t>The final present target price is calculated using a blended valuation approach. 
+Because Oracle is currently undergoing an unusually capital-intensive AI infrastructure investment cycle,the DCF valuation may understate the company’s long-term earnings power by heavily penalizing near-term free cash flow. Therefore, this model assigns a 25% weight to the DCF-derived present value and a 75% weight to the present value of the FY2029 P/E-based target price. This weighting reflects the view that forward earnings power is more representative of Oracle’s AI infrastructure monetization potential, while DCF remains useful as a conservative valuation cross-check.</t>
+  </si>
+  <si>
+    <t>Oracle Sensitivity Analysis</t>
+  </si>
+  <si>
+    <t>All values are formula-linked to the DCF sheet; no output values are hardcoded.</t>
+  </si>
+  <si>
+    <t>Bull Case - Blended Present Target Price</t>
+  </si>
+  <si>
+    <t>Current Check</t>
+  </si>
+  <si>
+    <t>Linked Formula</t>
+  </si>
+  <si>
+    <t>DCF Current</t>
+  </si>
+  <si>
+    <t>WACC \ Terminal Growth</t>
+  </si>
+  <si>
+    <t>Bull current</t>
+  </si>
+  <si>
+    <t>Base current</t>
+  </si>
+  <si>
+    <t>Bear current</t>
+  </si>
+  <si>
+    <t>Base Case - Blended Present Target Price</t>
+  </si>
+  <si>
+    <t>Bear Case - Blended Present Target Price</t>
+  </si>
+  <si>
+    <t>Blended Target Price</t>
+  </si>
+  <si>
+    <t>Comps Weight</t>
+  </si>
+  <si>
+    <t>DCF Weight</t>
+  </si>
+  <si>
+    <t>Present Value of Comps</t>
+  </si>
+  <si>
+    <t>Comps Target Price</t>
+  </si>
+  <si>
+    <t>Median Forward P/E</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>Workday</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ServiceNow</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>Oracle</t>
+  </si>
+  <si>
+    <t>Forward P/E</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2029 EPS </t>
+  </si>
+  <si>
+    <t>DCF Value</t>
+  </si>
+  <si>
+    <t>Note: EV/EBITDA target prices are FY2029 implied prices. Present values discount FY2029 prices back three years at the Cost of Equity.</t>
+  </si>
+  <si>
+    <t>EV/EBITDA Present Price</t>
+  </si>
+  <si>
+    <t>EV/EBITDA FY2029 Target Price</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Present EV/EBITDA Price</t>
+  </si>
+  <si>
+    <t>FY2029 Target Price</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Football Field Inputs</t>
+  </si>
+  <si>
+    <t>Present Value Bridge</t>
+  </si>
+  <si>
+    <t>Preferred Equity</t>
+  </si>
+  <si>
+    <t>Implied EV</t>
+  </si>
+  <si>
+    <t>FY2029 EBITDA</t>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+  </si>
+  <si>
+    <t>FY2029 EBIT</t>
+  </si>
+  <si>
+    <t>FY2029 Revenue</t>
+  </si>
+  <si>
+    <t>EV/EBITDA Multiple</t>
+  </si>
+  <si>
+    <t>EV/EBITDA Valuation (FY2029 Target Price)</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>EV/EBITDA</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>DCF+P/E Blend</t>
+  </si>
+  <si>
+    <t>DCF+ Trading Comps</t>
+  </si>
+  <si>
+    <t>The football field analysis suggests a valuation range of approximately $89–363 per share, with the blended base-case valuation centered around $220–240 per share, broadly consistent with Oracle's current market valuation while leaving meaningful upside  in the AI infrastructure bull case.</t>
+  </si>
+  <si>
     <t>Summary Box
 Rating : Initiating Coverage
-Current Price: TBD
-Target Price: TBD
-Upside: TBD
-Market Cap: TBD
-Sector: Software/ Cloud Infastructure</t>
-  </si>
-  <si>
-    <t>FY 2022</t>
-  </si>
-  <si>
-    <t>FY 2023</t>
-  </si>
-  <si>
-    <t>FY 2024</t>
-  </si>
-  <si>
-    <t>FY 2025</t>
-  </si>
-  <si>
-    <t>FY 2026</t>
-  </si>
-  <si>
-    <t>Income Statement</t>
-  </si>
-  <si>
-    <t>Revenue Growth</t>
-  </si>
-  <si>
-    <t>Cloud Services &amp; License Support</t>
-  </si>
-  <si>
-    <t>Cloud License &amp; On- Premise License</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Hardware</t>
-  </si>
-  <si>
-    <t>Services</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>Cloud/Software Operating Expense</t>
-  </si>
-  <si>
-    <t>Hardware Operating Expense</t>
-  </si>
-  <si>
-    <t>Services Operating Expense</t>
-  </si>
-  <si>
-    <t>Sales &amp; Marketing</t>
-  </si>
-  <si>
-    <t>R &amp; D</t>
-  </si>
-  <si>
-    <t>G &amp; A</t>
-  </si>
-  <si>
-    <t>Amortization of Intangibles</t>
-  </si>
-  <si>
-    <t>Acquistion/Restructuring/Other</t>
-  </si>
-  <si>
-    <t>Total Operating Expense</t>
-  </si>
-  <si>
-    <t>Operating Income/EBIT</t>
-  </si>
-  <si>
-    <t>Interest Expense</t>
-  </si>
-  <si>
-    <t>Non-operating Income/Expense</t>
-  </si>
-  <si>
-    <t>Income Before Tax</t>
-  </si>
-  <si>
-    <t>Tax Provision</t>
-  </si>
-  <si>
-    <t>Net Income</t>
-  </si>
-  <si>
-    <t>Preferred Dividends</t>
-  </si>
-  <si>
-    <t>Net Income to Common</t>
-  </si>
-  <si>
-    <t>Basic EPS</t>
-  </si>
-  <si>
-    <t>Diluted EPS</t>
-  </si>
-  <si>
-    <t>Basic Shares</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>USD millions</t>
-  </si>
-  <si>
-    <t>Diluted Shares</t>
-  </si>
-  <si>
-    <t>Balance Sheet</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>Cash and Cash Equivalents</t>
-  </si>
-  <si>
-    <t>Maketable Securities</t>
-  </si>
-  <si>
-    <t>Trade Receivables,net</t>
-  </si>
-  <si>
-    <t>Prepaid Expenses and Other Current Assets</t>
-  </si>
-  <si>
-    <t>Total Current Assets</t>
-  </si>
-  <si>
-    <t>PP&amp;E,net</t>
-  </si>
-  <si>
-    <t>Goodwill</t>
-  </si>
-  <si>
-    <t>Operating Lease right-of-use Assets</t>
-  </si>
-  <si>
-    <t>Deferred Tax Assets</t>
-  </si>
-  <si>
-    <t>Other Non-Current Assets</t>
-  </si>
-  <si>
-    <t>Total Non-Current Assets</t>
-  </si>
-  <si>
-    <t>Total Assets</t>
-  </si>
-  <si>
-    <t>Liabilities</t>
-  </si>
-  <si>
-    <t>Notes Payable and Other Borrowings, Current</t>
-  </si>
-  <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>Accrued Compensation and Related Benefits</t>
-  </si>
-  <si>
-    <t>Deferred Revenues</t>
-  </si>
-  <si>
-    <t>Other Current Liabilites</t>
-  </si>
-  <si>
-    <t>Total Current Liabilities</t>
-  </si>
-  <si>
-    <t>Notes Payable and Other Borrowings, Non-Current</t>
-  </si>
-  <si>
-    <t>Income Taxes Payable</t>
-  </si>
-  <si>
-    <t>Operating Lease Liabilities</t>
-  </si>
-  <si>
-    <t>Other Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>Total Liabilities</t>
-  </si>
-  <si>
-    <t>Total Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>Stockholders' Equity</t>
-  </si>
-  <si>
-    <t>Balance Sheet Check</t>
-  </si>
-  <si>
-    <t>Red : Wrong</t>
-  </si>
-  <si>
-    <t>Yellow : Right</t>
-  </si>
-  <si>
-    <t>Cash Flow Statement</t>
-  </si>
-  <si>
-    <t>Operating Activities</t>
-  </si>
-  <si>
-    <t>Depreciation</t>
-  </si>
-  <si>
-    <t>Deferred Income Taxes</t>
-  </si>
-  <si>
-    <t>Stock-Based Compensation/SBC</t>
-  </si>
-  <si>
-    <t>Other, net</t>
-  </si>
-  <si>
-    <t>Increase in Trade Receivables</t>
-  </si>
-  <si>
-    <t>Decrease in Prepaid &amp; Other Assets</t>
-  </si>
-  <si>
-    <t>Decrease in Income Taxes Payable</t>
-  </si>
-  <si>
-    <t>Decrease in AP &amp; Other Liabilities</t>
-  </si>
-  <si>
-    <t>Increase in Deferred Revenues</t>
-  </si>
-  <si>
-    <t>Customer Prepayments w/Significant Financing</t>
-  </si>
-  <si>
-    <t>Net Cash Provided by Operating Activities (OCF)</t>
-  </si>
-  <si>
-    <t>Investing Activities</t>
-  </si>
-  <si>
-    <t>Purchases of Marketable Securities &amp; Investments</t>
-  </si>
-  <si>
-    <t>Acquisition, Net of Cash Acquired</t>
-  </si>
-  <si>
-    <t>CapEx</t>
-  </si>
-  <si>
-    <t>Proceeds from Sales/Maturities of Investments</t>
-  </si>
-  <si>
-    <t>Net Cash Used/ Provided by Investing Activities</t>
-  </si>
-  <si>
-    <t>Financing Activities</t>
-  </si>
-  <si>
-    <t>Repurchase of Common Stock</t>
-  </si>
-  <si>
-    <t>Proceeds from Issurance of Common Stock</t>
-  </si>
-  <si>
-    <t>Tax Withholding on RSU Vesting RSU</t>
-  </si>
-  <si>
-    <t>Dividends Paid to Stockholders</t>
-  </si>
-  <si>
-    <t>Commercial Paper, Net</t>
-  </si>
-  <si>
-    <t>MCPS Issurance, Net</t>
-  </si>
-  <si>
-    <t>Short-Term Financing Activities, Net</t>
-  </si>
-  <si>
-    <t>Debt Issurance</t>
-  </si>
-  <si>
-    <t>Debt Repayment</t>
-  </si>
-  <si>
-    <t>Other Financing Activities,Net</t>
-  </si>
-  <si>
-    <t>Net Cash Provided/ Used by Financing Activities</t>
-  </si>
-  <si>
-    <t>FX Effect</t>
-  </si>
-  <si>
-    <t>Net Increase/ Decrease in Cash</t>
-  </si>
-  <si>
-    <t>Beginning Cash</t>
-  </si>
-  <si>
-    <t>Ending Cash</t>
-  </si>
-  <si>
-    <t>FCF</t>
-  </si>
-  <si>
-    <t>EBIT Margin</t>
-  </si>
-  <si>
-    <t>CapEx Margin</t>
-  </si>
-  <si>
-    <t>FY 2025A</t>
-  </si>
-  <si>
-    <t>FY 2024A</t>
-  </si>
-  <si>
-    <t>FY 2023A</t>
-  </si>
-  <si>
-    <t>FY 2022A</t>
-  </si>
-  <si>
-    <t>FY 2026A</t>
-  </si>
-  <si>
-    <t>FY 2027E</t>
-  </si>
-  <si>
-    <t>FY 2028E</t>
-  </si>
-  <si>
-    <t>FY 2029E</t>
-  </si>
-  <si>
-    <t>Tax Rate</t>
-  </si>
-  <si>
-    <t>D&amp;A Margin</t>
-  </si>
-  <si>
-    <t>Forecast Sheet</t>
-  </si>
-  <si>
-    <t>FY2027E</t>
-  </si>
-  <si>
-    <t>FY2028E</t>
-  </si>
-  <si>
-    <t>FY2029E</t>
-  </si>
-  <si>
-    <t>FY2026A</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>EBIT</t>
-  </si>
-  <si>
-    <t>OCF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest Expense </t>
-  </si>
-  <si>
-    <t>SBC Margin</t>
-  </si>
-  <si>
-    <t>Deferred Taxes M</t>
-  </si>
-  <si>
-    <t>ΔNWC</t>
-  </si>
-  <si>
-    <t>FY 2030E</t>
-  </si>
-  <si>
-    <t>FY 2031E</t>
-  </si>
-  <si>
-    <t>FY 2032E</t>
-  </si>
-  <si>
-    <t>WACC Calculation</t>
-  </si>
-  <si>
-    <t>Risk-Free Rate</t>
-  </si>
-  <si>
-    <t>Equity Risk Premium</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>Cost of Equity</t>
-  </si>
-  <si>
-    <t>Pre-tax Cost of Debt</t>
-  </si>
-  <si>
-    <t>After-tax Cost of Debt</t>
-  </si>
-  <si>
-    <t>Equity Weight</t>
-  </si>
-  <si>
-    <t>Debt Weight</t>
-  </si>
-  <si>
-    <t>WACC</t>
-  </si>
-  <si>
-    <t>Terminal Growth Rate</t>
-  </si>
-  <si>
-    <t>Terminal Value</t>
-  </si>
-  <si>
-    <t>Enterprise Value</t>
-  </si>
-  <si>
-    <t>Equity Value</t>
-  </si>
-  <si>
-    <t>Net Debt</t>
-  </si>
-  <si>
-    <t>Preferred  Equity</t>
-  </si>
-  <si>
-    <t>Present Target Price</t>
-  </si>
-  <si>
-    <t>EPS</t>
-  </si>
-  <si>
-    <t>P/E</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Bull Case</t>
-  </si>
-  <si>
-    <t>Base Case</t>
-  </si>
-  <si>
-    <t>Bear Case</t>
-  </si>
-  <si>
-    <t>Bull</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Bear</t>
-  </si>
-  <si>
-    <t>DCF Present Target Price</t>
-  </si>
-  <si>
-    <t>Present Value</t>
-  </si>
-  <si>
-    <t>The final present target price is calculated using a blended valuation approach. 
-Because Oracle is currently undergoing an unusually capital-intensive AI infrastructure investment cycle,the DCF valuation may understate the company’s long-term earnings power by heavily penalizing near-term free cash flow. Therefore, this model assigns a 25% weight to the DCF-derived present value and a 75% weight to the present value of the FY2029 P/E-based target price. This weighting reflects the view that forward earnings power is more representative of Oracle’s AI infrastructure monetization potential, while DCF remains useful as a conservative valuation cross-check.</t>
-  </si>
-  <si>
-    <t>Oracle Sensitivity Analysis</t>
-  </si>
-  <si>
-    <t>All values are formula-linked to the DCF sheet; no output values are hardcoded.</t>
-  </si>
-  <si>
-    <t>Bull Case - Blended Present Target Price</t>
-  </si>
-  <si>
-    <t>Current Check</t>
-  </si>
-  <si>
-    <t>Linked Formula</t>
-  </si>
-  <si>
-    <t>DCF Current</t>
-  </si>
-  <si>
-    <t>WACC \ Terminal Growth</t>
-  </si>
-  <si>
-    <t>Bull current</t>
-  </si>
-  <si>
-    <t>Base current</t>
-  </si>
-  <si>
-    <t>Bear current</t>
-  </si>
-  <si>
-    <t>Base Case - Blended Present Target Price</t>
-  </si>
-  <si>
-    <t>Bear Case - Blended Present Target Price</t>
-  </si>
-  <si>
-    <t>Blended Target Price</t>
-  </si>
-  <si>
-    <t>Comps Weight</t>
-  </si>
-  <si>
-    <t>DCF Weight</t>
-  </si>
-  <si>
-    <t>Present Value of Comps</t>
-  </si>
-  <si>
-    <t>Comps Target Price</t>
-  </si>
-  <si>
-    <t>Median Forward P/E</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>Workday</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>ServiceNow</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>SAP</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>Oracle</t>
-  </si>
-  <si>
-    <t>Forward P/E</t>
-  </si>
-  <si>
-    <t>Ticker</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2029 EPS </t>
-  </si>
-  <si>
-    <t>DCF Value</t>
-  </si>
-  <si>
-    <t>Note: EV/EBITDA target prices are FY2029 implied prices. Present values discount FY2029 prices back three years at the Cost of Equity.</t>
-  </si>
-  <si>
-    <t>EV/EBITDA Present Price</t>
-  </si>
-  <si>
-    <t>EV/EBITDA FY2029 Target Price</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Present EV/EBITDA Price</t>
-  </si>
-  <si>
-    <t>FY2029 Target Price</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Football Field Inputs</t>
-  </si>
-  <si>
-    <t>Present Value Bridge</t>
-  </si>
-  <si>
-    <t>Preferred Equity</t>
-  </si>
-  <si>
-    <t>Implied EV</t>
-  </si>
-  <si>
-    <t>FY2029 EBITDA</t>
-  </si>
-  <si>
-    <t>D&amp;A</t>
-  </si>
-  <si>
-    <t>FY2029 EBIT</t>
-  </si>
-  <si>
-    <t>FY2029 Revenue</t>
-  </si>
-  <si>
-    <t>EV/EBITDA Multiple</t>
-  </si>
-  <si>
-    <t>EV/EBITDA Valuation (FY2029 Target Price)</t>
-  </si>
-  <si>
-    <t>Mid</t>
-  </si>
-  <si>
-    <t>EV/EBITDA</t>
-  </si>
-  <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>DCF+P/E Blend</t>
-  </si>
-  <si>
-    <t>DCF+ Trading Comps</t>
-  </si>
-  <si>
-    <t>The football field analysis suggests a valuation range of approximately $89–363 per share, with the blended base-case valuation centered around $220–240 per share, broadly consistent with Oracle's current market valuation while leaving meaningful upside  in the AI infrastructure bull case.</t>
+Current Price: $141.60
+Target Price: $271.38
+Upside: 91.7%
+Market Cap: $408B
+FY End: May
+Sector: Technology
+Industry:
+Cloud Infrastructure &amp; Enterprise Software</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1370,6 +1373,21 @@
     <xf numFmtId="43" fontId="49" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1380,9 +1398,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1414,21 +1429,6 @@
     </xf>
     <xf numFmtId="8" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4954,15 +4954,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>352776</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>35277</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx4="http://schemas.microsoft.com/office/drawing/2016/5/10/chartex" Requires="cx4">
@@ -4998,8 +4998,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1" y="0"/>
-              <a:ext cx="6591299" cy="5537200"/>
+              <a:off x="0" y="0"/>
+              <a:ext cx="15169443" cy="13264444"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5031,16 +5031,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>111478</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>221545</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>35278</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5070,15 +5070,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:colOff>388056</xdr:colOff>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>166</xdr:row>
-      <xdr:rowOff>196850</xdr:rowOff>
+      <xdr:colOff>451556</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6114,720 +6114,797 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE6F2F2-24A5-AC4D-821B-50B424EDC4A8}">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="129" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-      <c r="R2" s="128"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="128"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
-      <c r="L3" s="128"/>
-      <c r="M3" s="128"/>
-      <c r="N3" s="128"/>
-      <c r="O3" s="128"/>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="128"/>
-      <c r="R3" s="128"/>
+      <c r="A3" s="113"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="128"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="128"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="128"/>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
+      <c r="A5" s="113"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="128"/>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128"/>
-      <c r="I6" s="128"/>
-      <c r="J6" s="128"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
-      <c r="M6" s="128"/>
-      <c r="N6" s="128"/>
-      <c r="O6" s="128"/>
-      <c r="P6" s="128"/>
-      <c r="Q6" s="128"/>
-      <c r="R6" s="128"/>
+      <c r="A6" s="113"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="113"/>
+      <c r="R6" s="113"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="128"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="128"/>
-      <c r="L7" s="128"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="128"/>
-      <c r="O7" s="128"/>
-      <c r="P7" s="128"/>
-      <c r="Q7" s="128"/>
-      <c r="R7" s="128"/>
+      <c r="A7" s="113"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="113"/>
+      <c r="R7" s="113"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="128"/>
-      <c r="B8" s="128"/>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="128"/>
-      <c r="H8" s="128"/>
-      <c r="I8" s="128"/>
-      <c r="J8" s="128"/>
-      <c r="K8" s="128"/>
-      <c r="L8" s="128"/>
-      <c r="M8" s="128"/>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="128"/>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
+      <c r="A8" s="113"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="128"/>
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128"/>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
+      <c r="A9" s="113"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="128"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="128"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="128"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="128"/>
-      <c r="N11" s="130" t="s">
-        <v>2</v>
-      </c>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="131"/>
-      <c r="R11" s="131"/>
+      <c r="A10" s="113"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="113"/>
+      <c r="N10" s="113"/>
+      <c r="O10" s="113"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+    </row>
+    <row r="11" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="113"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="115" t="s">
+        <v>220</v>
+      </c>
+      <c r="O11" s="115"/>
+      <c r="P11" s="115"/>
+      <c r="Q11" s="115"/>
+      <c r="R11" s="115"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="128"/>
-      <c r="B12" s="128"/>
-      <c r="C12" s="128"/>
-      <c r="D12" s="128"/>
-      <c r="E12" s="128"/>
-      <c r="F12" s="128"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="128"/>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="131"/>
+      <c r="A12" s="113"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="115"/>
+      <c r="O12" s="115"/>
+      <c r="P12" s="115"/>
+      <c r="Q12" s="115"/>
+      <c r="R12" s="115"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="128"/>
-      <c r="B13" s="128"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="131"/>
+      <c r="A13" s="113"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="113"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="128"/>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="128"/>
-      <c r="L14" s="128"/>
-      <c r="M14" s="128"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="131"/>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="131"/>
+      <c r="A14" s="113"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="128"/>
-      <c r="B15" s="128"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="128"/>
-      <c r="L15" s="128"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="131"/>
+      <c r="A15" s="113"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="113"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="115"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="128"/>
-      <c r="B16" s="128"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
-      <c r="M16" s="128"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="131"/>
+      <c r="A16" s="113"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="115"/>
+      <c r="R16" s="115"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="128"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="131"/>
+      <c r="A17" s="113"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="115"/>
+      <c r="P17" s="115"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="115"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="128"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="128"/>
-      <c r="L18" s="128"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="131"/>
-      <c r="O18" s="131"/>
-      <c r="P18" s="131"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="131"/>
+      <c r="A18" s="113"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="115"/>
+      <c r="Q18" s="115"/>
+      <c r="R18" s="115"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="128"/>
-      <c r="B19" s="128"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="131"/>
-      <c r="O19" s="131"/>
-      <c r="P19" s="131"/>
-      <c r="Q19" s="131"/>
-      <c r="R19" s="131"/>
+      <c r="A19" s="113"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="113"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="115"/>
+      <c r="Q19" s="115"/>
+      <c r="R19" s="115"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="128"/>
-      <c r="B20" s="128"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="128"/>
-      <c r="L20" s="128"/>
-      <c r="M20" s="128"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="131"/>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="131"/>
-      <c r="R20" s="131"/>
+      <c r="A20" s="113"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="113"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="115"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="115"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="128"/>
-      <c r="B21" s="128"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="128"/>
-      <c r="I21" s="128"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="128"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="128"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="131"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="128"/>
-      <c r="B22" s="128"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="128"/>
-      <c r="J22" s="128"/>
-      <c r="K22" s="128"/>
-      <c r="L22" s="128"/>
-      <c r="M22" s="128"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
-      <c r="P22" s="131"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
+      <c r="A22" s="113"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="128"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="128"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="113"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="115"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="128"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="128"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="128"/>
-      <c r="N24" s="131"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="131"/>
+      <c r="A24" s="113"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="113"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="113"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="113"/>
+      <c r="N24" s="115"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="115"/>
+      <c r="Q24" s="115"/>
+      <c r="R24" s="115"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="128"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="128"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="128"/>
-      <c r="K25" s="128"/>
-      <c r="L25" s="128"/>
-      <c r="M25" s="128"/>
-      <c r="N25" s="131"/>
-      <c r="O25" s="131"/>
-      <c r="P25" s="131"/>
-      <c r="Q25" s="131"/>
-      <c r="R25" s="131"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="115"/>
+      <c r="Q25" s="115"/>
+      <c r="R25" s="115"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="128"/>
-      <c r="B26" s="128"/>
-      <c r="C26" s="128"/>
-      <c r="D26" s="128"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="128"/>
-      <c r="G26" s="128"/>
-      <c r="H26" s="128"/>
-      <c r="I26" s="128"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="128"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="128"/>
-      <c r="N26" s="131"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="131"/>
-      <c r="Q26" s="131"/>
-      <c r="R26" s="131"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="115"/>
+      <c r="Q26" s="115"/>
+      <c r="R26" s="115"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="128"/>
-      <c r="B27" s="128"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="128"/>
-      <c r="F27" s="128"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="128"/>
-      <c r="I27" s="128"/>
-      <c r="J27" s="128"/>
-      <c r="K27" s="128"/>
-      <c r="L27" s="128"/>
-      <c r="M27" s="128"/>
-      <c r="N27" s="131"/>
-      <c r="O27" s="131"/>
-      <c r="P27" s="131"/>
-      <c r="Q27" s="131"/>
-      <c r="R27" s="131"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="115"/>
+      <c r="Q27" s="115"/>
+      <c r="R27" s="115"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="128"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="128"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="131"/>
-      <c r="O28" s="131"/>
-      <c r="P28" s="131"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="131"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="115"/>
+      <c r="R28" s="115"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="128"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="128"/>
-      <c r="L29" s="128"/>
-      <c r="M29" s="128"/>
-      <c r="N29" s="131"/>
-      <c r="O29" s="131"/>
-      <c r="P29" s="131"/>
-      <c r="Q29" s="131"/>
-      <c r="R29" s="131"/>
+      <c r="A29" s="113"/>
+      <c r="B29" s="113"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="113"/>
+      <c r="I29" s="113"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="115"/>
+      <c r="O29" s="115"/>
+      <c r="P29" s="115"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="115"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="128"/>
-      <c r="B30" s="128"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="128"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="128"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="128"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="131"/>
-      <c r="O30" s="131"/>
-      <c r="P30" s="131"/>
-      <c r="Q30" s="131"/>
-      <c r="R30" s="131"/>
+      <c r="A30" s="113"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="113"/>
+      <c r="N30" s="115"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="115"/>
+      <c r="R30" s="115"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="128"/>
-      <c r="B31" s="128"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="128"/>
-      <c r="F31" s="128"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
-      <c r="P31" s="131"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="131"/>
+      <c r="A31" s="113"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="115"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="115"/>
+      <c r="Q31" s="115"/>
+      <c r="R31" s="115"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="128"/>
-      <c r="B32" s="128"/>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
-      <c r="F32" s="128"/>
-      <c r="G32" s="128"/>
-      <c r="H32" s="128"/>
-      <c r="I32" s="128"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="131"/>
-      <c r="P32" s="131"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="131"/>
+      <c r="A32" s="113"/>
+      <c r="B32" s="113"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113"/>
+      <c r="N32" s="115"/>
+      <c r="O32" s="115"/>
+      <c r="P32" s="115"/>
+      <c r="Q32" s="115"/>
+      <c r="R32" s="115"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A33" s="128"/>
-      <c r="B33" s="128"/>
-      <c r="C33" s="128"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
-      <c r="M33" s="128"/>
-      <c r="N33" s="131"/>
-      <c r="O33" s="131"/>
-      <c r="P33" s="131"/>
-      <c r="Q33" s="131"/>
-      <c r="R33" s="131"/>
+      <c r="A33" s="113"/>
+      <c r="B33" s="113"/>
+      <c r="C33" s="113"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="115"/>
+      <c r="O33" s="115"/>
+      <c r="P33" s="115"/>
+      <c r="Q33" s="115"/>
+      <c r="R33" s="115"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34" s="128"/>
-      <c r="B34" s="128"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="128"/>
-      <c r="E34" s="128"/>
-      <c r="F34" s="128"/>
-      <c r="G34" s="128"/>
-      <c r="H34" s="128"/>
-      <c r="I34" s="128"/>
-      <c r="J34" s="128"/>
-      <c r="K34" s="128"/>
-      <c r="L34" s="128"/>
-      <c r="M34" s="128"/>
-      <c r="N34" s="131"/>
-      <c r="O34" s="131"/>
-      <c r="P34" s="131"/>
-      <c r="Q34" s="131"/>
-      <c r="R34" s="131"/>
+      <c r="A34" s="113"/>
+      <c r="B34" s="113"/>
+      <c r="C34" s="113"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="113"/>
+      <c r="M34" s="113"/>
+      <c r="N34" s="115"/>
+      <c r="O34" s="115"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="115"/>
+      <c r="R34" s="115"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A35" s="128"/>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="131"/>
-      <c r="O35" s="131"/>
-      <c r="P35" s="131"/>
-      <c r="Q35" s="131"/>
-      <c r="R35" s="131"/>
+      <c r="A35" s="113"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="113"/>
+      <c r="J35" s="113"/>
+      <c r="K35" s="113"/>
+      <c r="L35" s="113"/>
+      <c r="M35" s="113"/>
+      <c r="N35" s="115"/>
+      <c r="O35" s="115"/>
+      <c r="P35" s="115"/>
+      <c r="Q35" s="115"/>
+      <c r="R35" s="115"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N36" s="115"/>
+      <c r="O36" s="115"/>
+      <c r="P36" s="115"/>
+      <c r="Q36" s="115"/>
+      <c r="R36" s="115"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N37" s="115"/>
+      <c r="O37" s="115"/>
+      <c r="P37" s="115"/>
+      <c r="Q37" s="115"/>
+      <c r="R37" s="115"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N38" s="115"/>
+      <c r="O38" s="115"/>
+      <c r="P38" s="115"/>
+      <c r="Q38" s="115"/>
+      <c r="R38" s="115"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N39" s="115"/>
+      <c r="O39" s="115"/>
+      <c r="P39" s="115"/>
+      <c r="Q39" s="115"/>
+      <c r="R39" s="115"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N40" s="115"/>
+      <c r="O40" s="115"/>
+      <c r="P40" s="115"/>
+      <c r="Q40" s="115"/>
+      <c r="R40" s="115"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N41" s="115"/>
+      <c r="O41" s="115"/>
+      <c r="P41" s="115"/>
+      <c r="Q41" s="115"/>
+      <c r="R41" s="115"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N42" s="115"/>
+      <c r="O42" s="115"/>
+      <c r="P42" s="115"/>
+      <c r="Q42" s="115"/>
+      <c r="R42" s="115"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N43" s="115"/>
+      <c r="O43" s="115"/>
+      <c r="P43" s="115"/>
+      <c r="Q43" s="115"/>
+      <c r="R43" s="115"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N44" s="115"/>
+      <c r="O44" s="115"/>
+      <c r="P44" s="115"/>
+      <c r="Q44" s="115"/>
+      <c r="R44" s="115"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N45" s="115"/>
+      <c r="O45" s="115"/>
+      <c r="P45" s="115"/>
+      <c r="Q45" s="115"/>
+      <c r="R45" s="115"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N46" s="115"/>
+      <c r="O46" s="115"/>
+      <c r="P46" s="115"/>
+      <c r="Q46" s="115"/>
+      <c r="R46" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:M35"/>
     <mergeCell ref="N1:R10"/>
-    <mergeCell ref="N11:R35"/>
+    <mergeCell ref="N11:R46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6842,30 +6919,30 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="116"/>
       <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="116"/>
       <c r="B2" s="116"/>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>30174</v>
@@ -6886,13 +6963,13 @@
     </row>
     <row r="3" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3">
         <v>5878</v>
@@ -6913,7 +6990,7 @@
     </row>
     <row r="4" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
@@ -6934,7 +7011,7 @@
     </row>
     <row r="5" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -6955,7 +7032,7 @@
     </row>
     <row r="6" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3">
         <v>3183</v>
@@ -6976,7 +7053,7 @@
     </row>
     <row r="7" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
         <v>3205</v>
@@ -6997,7 +7074,7 @@
     </row>
     <row r="8" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
         <f>SUM(D2:D7)</f>
@@ -7023,7 +7100,7 @@
     </row>
     <row r="9" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="3">
         <v>-5213</v>
@@ -7044,7 +7121,7 @@
     </row>
     <row r="10" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3">
         <v>-972</v>
@@ -7065,7 +7142,7 @@
     </row>
     <row r="11" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3">
         <v>-2692</v>
@@ -7086,7 +7163,7 @@
     </row>
     <row r="12" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3">
         <v>-8047</v>
@@ -7107,7 +7184,7 @@
     </row>
     <row r="13" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3">
         <v>-7219</v>
@@ -7128,7 +7205,7 @@
     </row>
     <row r="14" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3">
         <v>-1317</v>
@@ -7149,7 +7226,7 @@
     </row>
     <row r="15" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3">
         <v>-1150</v>
@@ -7170,7 +7247,7 @@
     </row>
     <row r="16" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3">
         <v>-4904</v>
@@ -7191,7 +7268,7 @@
     </row>
     <row r="17" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
         <f>SUM(D9:D16)</f>
@@ -7217,7 +7294,7 @@
     </row>
     <row r="18" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
         <f>SUM(D17,D8)</f>
@@ -7243,7 +7320,7 @@
     </row>
     <row r="19" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="3">
         <v>-2755</v>
@@ -7264,7 +7341,7 @@
     </row>
     <row r="20" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3">
         <v>-522</v>
@@ -7285,7 +7362,7 @@
     </row>
     <row r="21" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(D18:D20)</f>
@@ -7311,7 +7388,7 @@
     </row>
     <row r="22" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="3">
         <v>-932</v>
@@ -7332,7 +7409,7 @@
     </row>
     <row r="23" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
         <f>SUM(D21:D22)</f>
@@ -7358,7 +7435,7 @@
     </row>
     <row r="24" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
@@ -7377,7 +7454,7 @@
     </row>
     <row r="25" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="3">
         <f>D23-D24</f>
@@ -7403,7 +7480,7 @@
     </row>
     <row r="26" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" s="7">
         <f>D25/D28</f>
@@ -7429,7 +7506,7 @@
     </row>
     <row r="27" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27" s="7">
         <f>D25/D29</f>
@@ -7455,7 +7532,7 @@
     </row>
     <row r="28" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" s="3">
         <v>2700</v>
@@ -7476,7 +7553,7 @@
     </row>
     <row r="29" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3">
         <v>2786</v>
@@ -7506,7 +7583,7 @@
     </row>
     <row r="31" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="116"/>
       <c r="C31" s="1"/>
@@ -7520,13 +7597,13 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
@@ -7544,7 +7621,7 @@
     </row>
     <row r="35" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="15">
@@ -7556,7 +7633,7 @@
     </row>
     <row r="36" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15">
@@ -7568,7 +7645,7 @@
     </row>
     <row r="37" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="15">
@@ -7580,7 +7657,7 @@
     </row>
     <row r="38" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="15">
@@ -7592,7 +7669,7 @@
     </row>
     <row r="39" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="18">
@@ -7605,7 +7682,7 @@
     </row>
     <row r="40" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="15">
@@ -7617,7 +7694,7 @@
     </row>
     <row r="41" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C41" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" s="15"/>
       <c r="E41" s="15">
@@ -7629,7 +7706,7 @@
     </row>
     <row r="42" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" s="15"/>
       <c r="E42" s="15">
@@ -7641,7 +7718,7 @@
     </row>
     <row r="43" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" s="15"/>
       <c r="E43" s="15">
@@ -7653,7 +7730,7 @@
     </row>
     <row r="44" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="15">
@@ -7665,7 +7742,7 @@
     </row>
     <row r="45" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18">
@@ -7678,7 +7755,7 @@
     </row>
     <row r="46" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18">
@@ -7699,7 +7776,7 @@
     </row>
     <row r="48" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="15"/>
@@ -7709,7 +7786,7 @@
     </row>
     <row r="49" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C49" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15">
@@ -7721,7 +7798,7 @@
     </row>
     <row r="50" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D50" s="15"/>
       <c r="E50" s="15">
@@ -7733,7 +7810,7 @@
     </row>
     <row r="51" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="15">
@@ -7745,7 +7822,7 @@
     </row>
     <row r="52" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15">
@@ -7757,7 +7834,7 @@
     </row>
     <row r="53" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15">
@@ -7769,7 +7846,7 @@
     </row>
     <row r="54" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="18">
@@ -7782,7 +7859,7 @@
     </row>
     <row r="55" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="15">
@@ -7794,7 +7871,7 @@
     </row>
     <row r="56" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" s="15"/>
       <c r="E56" s="15">
@@ -7806,7 +7883,7 @@
     </row>
     <row r="57" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="15">
@@ -7818,7 +7895,7 @@
     </row>
     <row r="58" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="15">
@@ -7830,7 +7907,7 @@
     </row>
     <row r="59" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="18">
@@ -7843,7 +7920,7 @@
     </row>
     <row r="60" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" s="18"/>
       <c r="E60" s="18">
@@ -7863,7 +7940,7 @@
     </row>
     <row r="62" spans="3:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D62" s="18"/>
       <c r="E62" s="18">
@@ -7917,7 +7994,7 @@
       <c r="C68" s="14"/>
       <c r="D68" s="9"/>
       <c r="E68" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F68" s="9"/>
       <c r="G68" s="4"/>
@@ -7925,14 +8002,14 @@
     </row>
     <row r="69" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="21">
         <f>E46-E60-E62</f>
         <v>0</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="4"/>
@@ -7967,11 +8044,11 @@
     </row>
     <row r="74" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="116"/>
       <c r="C74" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
@@ -8004,26 +8081,26 @@
     </row>
     <row r="76" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="E76" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="F76" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="15" t="s">
+      <c r="G76" s="15" t="s">
         <v>6</v>
-      </c>
-      <c r="G76" s="15" t="s">
-        <v>7</v>
       </c>
       <c r="H76" s="10"/>
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B77" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
@@ -8035,7 +8112,7 @@
     </row>
     <row r="78" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C78" s="15">
         <f>D23</f>
@@ -8062,7 +8139,7 @@
     </row>
     <row r="79" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="15">
         <v>1972</v>
@@ -8084,7 +8161,7 @@
     </row>
     <row r="80" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C80" s="15">
         <v>1150</v>
@@ -8106,7 +8183,7 @@
     </row>
     <row r="81" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C81" s="15">
         <v>-1146</v>
@@ -8128,7 +8205,7 @@
     </row>
     <row r="82" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C82" s="15">
         <v>2613</v>
@@ -8150,7 +8227,7 @@
     </row>
     <row r="83" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B83" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C83" s="15">
         <v>220</v>
@@ -8172,7 +8249,7 @@
     </row>
     <row r="84" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C84" s="15">
         <v>-874</v>
@@ -8194,7 +8271,7 @@
     </row>
     <row r="85" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C85" s="15">
         <v>11</v>
@@ -8216,7 +8293,7 @@
     </row>
     <row r="86" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C86" s="15">
         <v>-733</v>
@@ -8238,7 +8315,7 @@
     </row>
     <row r="87" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C87" s="15">
         <v>-398</v>
@@ -8260,7 +8337,7 @@
     </row>
     <row r="88" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C88" s="15">
         <v>7</v>
@@ -8282,7 +8359,7 @@
     </row>
     <row r="89" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C89" s="15">
         <v>0</v>
@@ -8304,7 +8381,7 @@
     </row>
     <row r="90" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C90" s="19">
         <f>SUM(C78:C89)</f>
@@ -8331,7 +8408,7 @@
     </row>
     <row r="91" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15"/>
@@ -8343,7 +8420,7 @@
     </row>
     <row r="92" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C92" s="15">
         <v>-10272</v>
@@ -8365,7 +8442,7 @@
     </row>
     <row r="93" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B93" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C93" s="15">
         <v>26151</v>
@@ -8387,7 +8464,7 @@
     </row>
     <row r="94" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C94" s="15">
         <v>-148</v>
@@ -8409,7 +8486,7 @@
     </row>
     <row r="95" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B95" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C95" s="29">
         <v>-4511</v>
@@ -8431,7 +8508,7 @@
     </row>
     <row r="96" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C96" s="19">
         <f>SUM(C92:C95)</f>
@@ -8458,7 +8535,7 @@
     </row>
     <row r="97" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B97" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="15"/>
@@ -8470,7 +8547,7 @@
     </row>
     <row r="98" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C98" s="15">
         <v>-16248</v>
@@ -8492,7 +8569,7 @@
     </row>
     <row r="99" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C99" s="15">
         <v>482</v>
@@ -8514,7 +8591,7 @@
     </row>
     <row r="100" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C100" s="15">
         <v>-1093</v>
@@ -8536,7 +8613,7 @@
     </row>
     <row r="101" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B101" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C101" s="15">
         <v>-3457</v>
@@ -8558,7 +8635,7 @@
     </row>
     <row r="102" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B102" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C102" s="15">
         <v>0</v>
@@ -8580,7 +8657,7 @@
     </row>
     <row r="103" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C103" s="15">
         <v>0</v>
@@ -8602,7 +8679,7 @@
     </row>
     <row r="104" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C104" s="15">
         <v>0</v>
@@ -8624,7 +8701,7 @@
     </row>
     <row r="105" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B105" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C105" s="15">
         <v>0</v>
@@ -8646,7 +8723,7 @@
     </row>
     <row r="106" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C106" s="15">
         <v>-8250</v>
@@ -8668,7 +8745,7 @@
     </row>
     <row r="107" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C107" s="15">
         <v>-560</v>
@@ -8690,7 +8767,7 @@
     </row>
     <row r="108" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C108" s="19">
         <f>SUM(C98:C107)</f>
@@ -8717,7 +8794,7 @@
     </row>
     <row r="109" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B109" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109" s="15">
         <v>-348</v>
@@ -8739,7 +8816,7 @@
     </row>
     <row r="110" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C110" s="18">
         <f>SUM(C108,C109,C96,C90)</f>
@@ -8766,7 +8843,7 @@
     </row>
     <row r="111" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C111" s="18">
         <v>30098</v>
@@ -8792,7 +8869,7 @@
     </row>
     <row r="112" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C112" s="18">
         <f>C111+C110</f>
@@ -8819,7 +8896,7 @@
     </row>
     <row r="113" spans="2:9" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C113" s="18">
         <f>C90+C95</f>
@@ -11303,32 +11380,32 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B1" s="116"/>
       <c r="C1" s="116"/>
       <c r="D1" s="116"/>
       <c r="E1" s="116"/>
       <c r="G1" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H1" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="J1" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="J1" s="39" t="s">
-        <v>122</v>
-      </c>
       <c r="K1" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="M1" s="39" t="s">
         <v>132</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>133</v>
       </c>
       <c r="N1" s="26"/>
     </row>
@@ -11339,7 +11416,7 @@
       <c r="D2" s="116"/>
       <c r="E2" s="116"/>
       <c r="F2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G2" s="15">
         <f>+'Historical Financials'!$H$8</f>
@@ -11370,7 +11447,7 @@
         <v>349942.09741946007</v>
       </c>
       <c r="N2" s="116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O2" s="116"/>
       <c r="P2" s="116"/>
@@ -11382,7 +11459,7 @@
       <c r="D3" s="116"/>
       <c r="E3" s="116"/>
       <c r="F3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G3" s="15">
         <f>+'Historical Financials'!$H$18</f>
@@ -11423,7 +11500,7 @@
       <c r="D4" s="116"/>
       <c r="E4" s="116"/>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="15">
         <f>+'Historical Financials'!$H$23</f>
@@ -11464,7 +11541,7 @@
       <c r="D5" s="116"/>
       <c r="E5" s="116"/>
       <c r="F5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G5" s="15">
         <f>+'Historical Financials'!$G$90</f>
@@ -11505,7 +11582,7 @@
       <c r="D6" s="116"/>
       <c r="E6" s="116"/>
       <c r="F6" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" s="15">
         <f>+'Historical Financials'!$G$95</f>
@@ -11544,7 +11621,7 @@
       <c r="D7" s="116"/>
       <c r="E7" s="116"/>
       <c r="F7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G7" s="15">
         <f>+'Historical Financials'!$G$113</f>
@@ -11704,30 +11781,30 @@
     </row>
     <row r="26" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G26" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H26" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I26" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="I26" s="39" t="s">
+      <c r="J26" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="J26" s="39" t="s">
-        <v>122</v>
-      </c>
       <c r="K26" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="L26" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="L26" s="39" t="s">
+      <c r="M26" s="39" t="s">
         <v>132</v>
-      </c>
-      <c r="M26" s="39" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F27" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G27" s="15">
         <f>+'Historical Financials'!$H$8</f>
@@ -11758,14 +11835,14 @@
         <v>208722.40945019992</v>
       </c>
       <c r="N27" s="116" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O27" s="116"/>
       <c r="P27" s="116"/>
     </row>
     <row r="28" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" s="15">
         <f>+'Historical Financials'!$H$18</f>
@@ -11801,7 +11878,7 @@
     </row>
     <row r="29" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" s="15">
         <f>+'Historical Financials'!$H$23</f>
@@ -11837,7 +11914,7 @@
     </row>
     <row r="30" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G30" s="15">
         <f>+'Historical Financials'!$G$90</f>
@@ -11873,7 +11950,7 @@
     </row>
     <row r="31" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G31" s="15">
         <f>+'Historical Financials'!$G$95</f>
@@ -11906,7 +11983,7 @@
     </row>
     <row r="32" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G32" s="15">
         <f>+'Historical Financials'!$G$113</f>
@@ -11939,30 +12016,30 @@
     </row>
     <row r="48" spans="7:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G48" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H48" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I48" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="I48" s="39" t="s">
+      <c r="J48" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="J48" s="39" t="s">
-        <v>122</v>
-      </c>
       <c r="K48" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="L48" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="L48" s="39" t="s">
+      <c r="M48" s="39" t="s">
         <v>132</v>
-      </c>
-      <c r="M48" s="39" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="49" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G49" s="15">
         <f>+'Historical Financials'!$H$8</f>
@@ -11993,14 +12070,14 @@
         <v>160367.35127050002</v>
       </c>
       <c r="N49" s="116" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
     </row>
     <row r="50" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G50" s="15">
         <f>+'Historical Financials'!$H$18</f>
@@ -12036,7 +12113,7 @@
     </row>
     <row r="51" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" s="15">
         <f>+'Historical Financials'!$H$23</f>
@@ -12072,7 +12149,7 @@
     </row>
     <row r="52" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F52" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G52" s="15">
         <f>+'Historical Financials'!$G$90</f>
@@ -12108,7 +12185,7 @@
     </row>
     <row r="53" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F53" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G53" s="15">
         <f>+'Historical Financials'!$G$95</f>
@@ -12141,7 +12218,7 @@
     </row>
     <row r="54" spans="6:16" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F54" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G54" s="15">
         <f>+'Historical Financials'!$G$113</f>
@@ -12174,7 +12251,7 @@
     </row>
     <row r="76" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B76" s="116"/>
       <c r="C76" s="30"/>
@@ -12227,37 +12304,37 @@
     <row r="81" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G81" s="40" t="s">
+      <c r="H81" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="H81" s="40" t="s">
+      <c r="I81" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="I81" s="40" t="s">
-        <v>116</v>
-      </c>
       <c r="J81" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="K81" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="K81" s="40" t="s">
+      <c r="L81" s="40" t="s">
         <v>132</v>
-      </c>
-      <c r="L81" s="40" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -12276,7 +12353,7 @@
     </row>
     <row r="83" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B83" s="37"/>
       <c r="C83" s="37">
@@ -12312,7 +12389,7 @@
     </row>
     <row r="84" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B84" s="37">
         <v>0.25744580584354382</v>
@@ -12350,7 +12427,7 @@
     </row>
     <row r="85" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" s="37">
         <v>0.10629123468426013</v>
@@ -12388,7 +12465,7 @@
     </row>
     <row r="86" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" s="37">
         <v>0.12184599294025363</v>
@@ -12426,7 +12503,7 @@
     </row>
     <row r="87" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B87" s="37">
         <v>7.3562676720075396E-2</v>
@@ -12464,7 +12541,7 @@
     </row>
     <row r="88" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B88" s="37">
         <v>6.4915174363807726E-2</v>
@@ -12502,7 +12579,7 @@
     </row>
     <row r="89" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B89" s="37">
         <v>6.1569274269557023E-2</v>
@@ -12540,7 +12617,7 @@
     </row>
     <row r="90" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B90" s="37">
         <v>2.7002827521206408E-2</v>
@@ -12578,7 +12655,7 @@
     </row>
     <row r="91" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B91" s="37">
         <v>-4.6819038642789822E-2</v>
@@ -12626,7 +12703,7 @@
     </row>
     <row r="101" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="116" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B101" s="116"/>
       <c r="C101" s="30"/>
@@ -12679,37 +12756,37 @@
     <row r="106" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G106" s="40" t="s">
+      <c r="H106" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="H106" s="40" t="s">
+      <c r="I106" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="I106" s="40" t="s">
-        <v>116</v>
-      </c>
       <c r="J106" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="K106" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="K106" s="40" t="s">
+      <c r="L106" s="40" t="s">
         <v>132</v>
-      </c>
-      <c r="L106" s="40" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -12728,7 +12805,7 @@
     </row>
     <row r="108" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B108" s="37"/>
       <c r="C108" s="37">
@@ -12764,7 +12841,7 @@
     </row>
     <row r="109" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109" s="37">
         <v>0.25744580584354382</v>
@@ -12802,7 +12879,7 @@
     </row>
     <row r="110" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B110" s="37">
         <v>0.10629123468426013</v>
@@ -12840,7 +12917,7 @@
     </row>
     <row r="111" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B111" s="37">
         <v>0.12184599294025363</v>
@@ -12878,7 +12955,7 @@
     </row>
     <row r="112" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B112" s="37">
         <v>7.3562676720075396E-2</v>
@@ -12916,7 +12993,7 @@
     </row>
     <row r="113" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B113" s="37">
         <v>6.4915174363807726E-2</v>
@@ -12954,7 +13031,7 @@
     </row>
     <row r="114" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B114" s="37">
         <v>6.1569274269557023E-2</v>
@@ -12992,7 +13069,7 @@
     </row>
     <row r="115" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B115" s="37">
         <v>2.7002827521206408E-2</v>
@@ -13030,7 +13107,7 @@
     </row>
     <row r="116" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B116" s="37">
         <v>-4.6819038642789822E-2</v>
@@ -13068,7 +13145,7 @@
     </row>
     <row r="123" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="116" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B123" s="116"/>
       <c r="C123" s="30"/>
@@ -13141,37 +13218,37 @@
     <row r="128" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="31"/>
       <c r="B128" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D128" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F128" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="C128" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D128" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E128" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="F128" s="31" t="s">
+      <c r="G128" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="G128" s="52" t="s">
+      <c r="H128" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="H128" s="52" t="s">
+      <c r="I128" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="I128" s="52" t="s">
-        <v>116</v>
-      </c>
       <c r="J128" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="K128" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="K128" s="52" t="s">
+      <c r="L128" s="52" t="s">
         <v>132</v>
-      </c>
-      <c r="L128" s="52" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -13190,7 +13267,7 @@
     </row>
     <row r="130" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B130" s="56"/>
       <c r="C130" s="56">
@@ -13226,7 +13303,7 @@
     </row>
     <row r="131" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B131" s="56">
         <v>0.25740000000000002</v>
@@ -13264,7 +13341,7 @@
     </row>
     <row r="132" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B132" s="56">
         <v>0.10630000000000001</v>
@@ -13302,7 +13379,7 @@
     </row>
     <row r="133" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B133" s="56">
         <v>0.12180000000000001</v>
@@ -13340,7 +13417,7 @@
     </row>
     <row r="134" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B134" s="56">
         <v>7.3599999999999999E-2</v>
@@ -13378,7 +13455,7 @@
     </row>
     <row r="135" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B135" s="56">
         <v>6.4899999999999999E-2</v>
@@ -13416,7 +13493,7 @@
     </row>
     <row r="136" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B136" s="56">
         <v>6.1600000000000002E-2</v>
@@ -13454,7 +13531,7 @@
     </row>
     <row r="137" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B137" s="56">
         <v>2.7E-2</v>
@@ -13492,7 +13569,7 @@
     </row>
     <row r="138" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B138" s="56">
         <v>-4.6800000000000001E-2</v>
@@ -13569,7 +13646,7 @@
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" s="116"/>
       <c r="C2" s="116"/>
@@ -13578,14 +13655,14 @@
       <c r="F2" s="62"/>
       <c r="G2" s="62"/>
       <c r="H2" s="45"/>
-      <c r="I2" s="124" t="s">
-        <v>162</v>
-      </c>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
+      <c r="I2" s="128" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
       <c r="P2" s="79"/>
       <c r="Q2" s="79"/>
       <c r="R2" s="41"/>
@@ -13602,12 +13679,12 @@
       <c r="F3" s="62"/>
       <c r="G3" s="62"/>
       <c r="H3" s="45"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
       <c r="P3" s="79"/>
       <c r="Q3" s="79"/>
       <c r="R3" s="41"/>
@@ -13623,12 +13700,12 @@
       <c r="E4" s="62"/>
       <c r="F4" s="62"/>
       <c r="G4" s="62"/>
-      <c r="I4" s="124"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
       <c r="P4" s="79"/>
       <c r="Q4" s="79"/>
       <c r="R4" s="41"/>
@@ -13638,7 +13715,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" s="37">
         <v>4.4999999999999998E-2</v>
@@ -13646,12 +13723,12 @@
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
       <c r="E5" s="45"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="128"/>
       <c r="P5" s="79"/>
       <c r="Q5" s="79"/>
       <c r="R5" s="41"/>
@@ -13661,7 +13738,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B6" s="37">
         <v>5.5E-2</v>
@@ -13669,12 +13746,12 @@
       <c r="C6" s="37"/>
       <c r="D6" s="37"/>
       <c r="E6" s="45"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="124"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
+      <c r="M6" s="128"/>
+      <c r="N6" s="128"/>
       <c r="O6" s="79"/>
       <c r="P6" s="79"/>
       <c r="Q6" s="79"/>
@@ -13685,7 +13762,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" s="47">
         <v>1.25</v>
@@ -13696,12 +13773,12 @@
       <c r="F7" s="63"/>
       <c r="G7" s="63"/>
       <c r="H7" s="45"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="128"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="128"/>
       <c r="O7" s="79"/>
       <c r="P7" s="79"/>
       <c r="Q7" s="79"/>
@@ -13712,7 +13789,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="37">
         <v>0.11375</v>
@@ -13723,12 +13800,12 @@
       <c r="F8" s="63"/>
       <c r="G8" s="63"/>
       <c r="H8" s="45"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="128"/>
+      <c r="N8" s="128"/>
       <c r="O8" s="79"/>
       <c r="P8" s="79"/>
       <c r="Q8" s="79"/>
@@ -13739,7 +13816,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B9" s="37">
         <v>5.5E-2</v>
@@ -13750,12 +13827,12 @@
       <c r="F9" s="63"/>
       <c r="G9" s="63"/>
       <c r="H9" s="45"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
       <c r="O9" s="79"/>
       <c r="P9" s="79"/>
       <c r="Q9" s="79"/>
@@ -13766,7 +13843,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="37">
         <v>0.13</v>
@@ -13777,12 +13854,12 @@
       <c r="F10" s="45"/>
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
       <c r="O10" s="79"/>
       <c r="P10" s="79"/>
       <c r="Q10" s="79"/>
@@ -13793,7 +13870,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B11" s="37">
         <v>4.7849999999999997E-2</v>
@@ -13804,12 +13881,12 @@
       <c r="F11" s="45"/>
       <c r="G11" s="45"/>
       <c r="H11" s="45"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="124"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="128"/>
       <c r="O11" s="79"/>
       <c r="P11" s="79"/>
       <c r="Q11" s="79"/>
@@ -13820,7 +13897,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="37">
         <v>0.8</v>
@@ -13829,7 +13906,7 @@
       <c r="D12" s="37"/>
       <c r="E12" s="45"/>
       <c r="F12" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G12" s="74">
         <f>'Historical Financials'!E49+'Historical Financials'!E55-'Historical Financials'!G112</f>
@@ -13852,7 +13929,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="37">
         <v>0.2</v>
@@ -13861,7 +13938,7 @@
       <c r="D13" s="37"/>
       <c r="E13" s="45"/>
       <c r="F13" s="74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G13" s="74">
         <f>'Historical Financials'!G103</f>
@@ -13889,7 +13966,7 @@
       <c r="D14" s="37"/>
       <c r="E14" s="50"/>
       <c r="F14" s="74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="75">
         <v>2866</v>
@@ -13911,7 +13988,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15" s="37">
         <f>B13*B9*(1-B10)+B12*(B5+B7*B6)</f>
@@ -13938,7 +14015,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" s="37">
         <v>0.04</v>
@@ -13970,13 +14047,13 @@
     <row r="17" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="D17" s="37" t="s">
         <v>158</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>159</v>
       </c>
       <c r="E17" s="45"/>
       <c r="F17" s="45"/>
@@ -14042,7 +14119,7 @@
     </row>
     <row r="20" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
@@ -14068,28 +14145,28 @@
     <row r="21" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="E21" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="71" t="s">
-        <v>122</v>
-      </c>
       <c r="F21" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="72" t="s">
+      <c r="H21" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="H21" s="72" t="s">
-        <v>133</v>
-      </c>
       <c r="I21" s="45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J21" s="44"/>
       <c r="K21" s="44"/>
@@ -14106,7 +14183,7 @@
     </row>
     <row r="22" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B22" s="49">
         <v>67357</v>
@@ -14138,22 +14215,22 @@
       <c r="L22" s="44"/>
       <c r="M22" s="41"/>
       <c r="N22" s="116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O22" s="116"/>
       <c r="P22" s="116"/>
-      <c r="Q22" s="122">
+      <c r="Q22" s="126">
         <f>NPV(B15,C28:H28)</f>
         <v>670630.67454587424</v>
       </c>
-      <c r="R22" s="123"/>
-      <c r="S22" s="123"/>
+      <c r="R22" s="127"/>
+      <c r="S22" s="127"/>
       <c r="T22" s="41"/>
       <c r="U22" s="41"/>
     </row>
     <row r="23" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23" s="49">
         <v>20606</v>
@@ -14184,15 +14261,15 @@
       <c r="N23" s="116"/>
       <c r="O23" s="116"/>
       <c r="P23" s="116"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="123"/>
+      <c r="Q23" s="127"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="127"/>
       <c r="T23" s="41"/>
       <c r="U23" s="41"/>
     </row>
     <row r="24" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="49">
         <v>17087</v>
@@ -14217,7 +14294,7 @@
       </c>
       <c r="I24" s="48"/>
       <c r="J24" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="76">
@@ -14227,15 +14304,15 @@
       <c r="N24" s="116"/>
       <c r="O24" s="116"/>
       <c r="P24" s="116"/>
-      <c r="Q24" s="123"/>
-      <c r="R24" s="123"/>
-      <c r="S24" s="123"/>
+      <c r="Q24" s="127"/>
+      <c r="R24" s="127"/>
+      <c r="S24" s="127"/>
       <c r="T24" s="41"/>
       <c r="U24" s="41"/>
     </row>
     <row r="25" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B25" s="49">
         <v>31977</v>
@@ -14274,7 +14351,7 @@
     </row>
     <row r="26" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B26" s="49">
         <v>-55663</v>
@@ -14313,7 +14390,7 @@
     </row>
     <row r="27" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="49">
         <v>-23686</v>
@@ -14342,16 +14419,16 @@
       <c r="L27" s="45"/>
       <c r="M27" s="41"/>
       <c r="N27" s="116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O27" s="116"/>
       <c r="P27" s="116"/>
-      <c r="Q27" s="123">
+      <c r="Q27" s="127">
         <f>Q22-G12-G13</f>
         <v>567424.67454587424</v>
       </c>
-      <c r="R27" s="123"/>
-      <c r="S27" s="123"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
       <c r="T27" s="41"/>
       <c r="U27" s="41"/>
     </row>
@@ -14392,15 +14469,15 @@
       <c r="N28" s="116"/>
       <c r="O28" s="116"/>
       <c r="P28" s="116"/>
-      <c r="Q28" s="123"/>
-      <c r="R28" s="123"/>
-      <c r="S28" s="123"/>
+      <c r="Q28" s="127"/>
+      <c r="R28" s="127"/>
+      <c r="S28" s="127"/>
       <c r="T28" s="41"/>
       <c r="U28" s="41"/>
     </row>
     <row r="29" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="49">
         <f>'Historical Financials'!H29</f>
@@ -14426,26 +14503,26 @@
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K29" s="116"/>
-      <c r="L29" s="121">
+      <c r="L29" s="125">
         <f>L24*E30</f>
         <v>401.45596112894992</v>
       </c>
-      <c r="M29" s="121"/>
+      <c r="M29" s="125"/>
       <c r="N29" s="116"/>
       <c r="O29" s="116"/>
       <c r="P29" s="116"/>
-      <c r="Q29" s="123"/>
-      <c r="R29" s="123"/>
-      <c r="S29" s="123"/>
+      <c r="Q29" s="127"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
       <c r="T29" s="41"/>
       <c r="U29" s="41"/>
     </row>
     <row r="30" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1">
         <f>B24/B29</f>
@@ -14477,8 +14554,8 @@
       </c>
       <c r="J30" s="116"/>
       <c r="K30" s="116"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="125"/>
       <c r="N30" s="41"/>
       <c r="O30" s="41"/>
       <c r="P30" s="41"/>
@@ -14487,7 +14564,7 @@
       <c r="S30" s="41"/>
       <c r="T30" s="41"/>
       <c r="U30" s="116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V30" s="116"/>
       <c r="W30" s="116"/>
@@ -14496,8 +14573,8 @@
     <row r="31" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J31" s="116"/>
       <c r="K31" s="116"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="121"/>
+      <c r="L31" s="125"/>
+      <c r="M31" s="125"/>
       <c r="N31" s="41"/>
       <c r="O31" s="41"/>
       <c r="P31" s="41"/>
@@ -14509,12 +14586,12 @@
       <c r="V31" s="116"/>
       <c r="W31" s="116"/>
       <c r="X31" s="116"/>
-      <c r="Z31" s="112">
+      <c r="Z31" s="117">
         <f>L32*0.75+Q33*0.25</f>
         <v>274.77947721044421</v>
       </c>
-      <c r="AA31" s="113"/>
-      <c r="AB31" s="113"/>
+      <c r="AA31" s="118"/>
+      <c r="AB31" s="118"/>
     </row>
     <row r="32" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="62"/>
@@ -14523,14 +14600,14 @@
       <c r="E32" s="45"/>
       <c r="F32" s="45"/>
       <c r="J32" s="116" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K32" s="116"/>
-      <c r="L32" s="119">
+      <c r="L32" s="123">
         <f>L29/(1+B15)^3</f>
         <v>301.1514093212964</v>
       </c>
-      <c r="M32" s="120"/>
+      <c r="M32" s="124"/>
       <c r="N32" s="41"/>
       <c r="O32" s="41"/>
       <c r="P32" s="41"/>
@@ -14542,9 +14619,9 @@
       <c r="V32" s="116"/>
       <c r="W32" s="116"/>
       <c r="X32" s="116"/>
-      <c r="Z32" s="113"/>
-      <c r="AA32" s="113"/>
-      <c r="AB32" s="113"/>
+      <c r="Z32" s="118"/>
+      <c r="AA32" s="118"/>
+      <c r="AB32" s="118"/>
     </row>
     <row r="33" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="62"/>
@@ -14554,27 +14631,27 @@
       <c r="F33" s="51"/>
       <c r="J33" s="116"/>
       <c r="K33" s="116"/>
-      <c r="L33" s="120"/>
-      <c r="M33" s="120"/>
+      <c r="L33" s="124"/>
+      <c r="M33" s="124"/>
       <c r="N33" s="116" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O33" s="116"/>
       <c r="P33" s="116"/>
-      <c r="Q33" s="121">
+      <c r="Q33" s="125">
         <f>Q27/E29</f>
         <v>195.66368087788766</v>
       </c>
-      <c r="R33" s="121"/>
-      <c r="S33" s="121"/>
+      <c r="R33" s="125"/>
+      <c r="S33" s="125"/>
       <c r="T33" s="41"/>
       <c r="U33" s="116"/>
       <c r="V33" s="116"/>
       <c r="W33" s="116"/>
       <c r="X33" s="116"/>
-      <c r="Z33" s="113"/>
-      <c r="AA33" s="113"/>
-      <c r="AB33" s="113"/>
+      <c r="Z33" s="118"/>
+      <c r="AA33" s="118"/>
+      <c r="AB33" s="118"/>
     </row>
     <row r="34" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="62"/>
@@ -14583,14 +14660,14 @@
       <c r="F34" s="51"/>
       <c r="J34" s="116"/>
       <c r="K34" s="116"/>
-      <c r="L34" s="120"/>
-      <c r="M34" s="120"/>
+      <c r="L34" s="124"/>
+      <c r="M34" s="124"/>
       <c r="N34" s="116"/>
       <c r="O34" s="116"/>
       <c r="P34" s="116"/>
-      <c r="Q34" s="121"/>
-      <c r="R34" s="121"/>
-      <c r="S34" s="121"/>
+      <c r="Q34" s="125"/>
+      <c r="R34" s="125"/>
+      <c r="S34" s="125"/>
       <c r="T34" s="41"/>
       <c r="U34" s="116"/>
       <c r="V34" s="116"/>
@@ -14601,9 +14678,9 @@
       <c r="N35" s="116"/>
       <c r="O35" s="116"/>
       <c r="P35" s="116"/>
-      <c r="Q35" s="121"/>
-      <c r="R35" s="121"/>
-      <c r="S35" s="121"/>
+      <c r="Q35" s="125"/>
+      <c r="R35" s="125"/>
+      <c r="S35" s="125"/>
       <c r="T35" s="41"/>
       <c r="U35" s="41"/>
     </row>
@@ -14619,9 +14696,9 @@
       <c r="N36" s="116"/>
       <c r="O36" s="116"/>
       <c r="P36" s="116"/>
-      <c r="Q36" s="121"/>
-      <c r="R36" s="121"/>
-      <c r="S36" s="121"/>
+      <c r="Q36" s="125"/>
+      <c r="R36" s="125"/>
+      <c r="S36" s="125"/>
       <c r="T36" s="41"/>
       <c r="U36" s="41"/>
     </row>
@@ -14675,51 +14752,51 @@
     </row>
     <row r="40" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="41"/>
       <c r="N40" s="116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="116"/>
       <c r="P40" s="116"/>
-      <c r="Q40" s="126">
+      <c r="Q40" s="130">
         <f>NPV(B15,C48:H48)</f>
         <v>338557.11712424085</v>
       </c>
-      <c r="R40" s="125"/>
-      <c r="S40" s="125"/>
+      <c r="R40" s="129"/>
+      <c r="S40" s="129"/>
       <c r="T40" s="41"/>
       <c r="U40" s="41"/>
     </row>
     <row r="41" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C41" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D41" s="70" t="s">
+      <c r="E41" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="E41" s="70" t="s">
-        <v>122</v>
-      </c>
       <c r="F41" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="G41" s="70" t="s">
+      <c r="H41" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="H41" s="70" t="s">
-        <v>133</v>
-      </c>
       <c r="I41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
@@ -14728,15 +14805,15 @@
       <c r="N41" s="116"/>
       <c r="O41" s="116"/>
       <c r="P41" s="116"/>
-      <c r="Q41" s="125"/>
-      <c r="R41" s="125"/>
-      <c r="S41" s="125"/>
+      <c r="Q41" s="129"/>
+      <c r="R41" s="129"/>
+      <c r="S41" s="129"/>
       <c r="T41" s="41"/>
       <c r="U41" s="41"/>
     </row>
     <row r="42" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B42" s="15">
         <v>67357</v>
@@ -14770,15 +14847,15 @@
       <c r="N42" s="116"/>
       <c r="O42" s="116"/>
       <c r="P42" s="116"/>
-      <c r="Q42" s="125"/>
-      <c r="R42" s="125"/>
-      <c r="S42" s="125"/>
+      <c r="Q42" s="129"/>
+      <c r="R42" s="129"/>
+      <c r="S42" s="129"/>
       <c r="T42" s="41"/>
       <c r="U42" s="41"/>
     </row>
     <row r="43" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" s="15">
         <v>20606</v>
@@ -14803,7 +14880,7 @@
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="76" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K43" s="76"/>
       <c r="L43" s="76">
@@ -14821,7 +14898,7 @@
     </row>
     <row r="44" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="15">
         <v>17087</v>
@@ -14860,7 +14937,7 @@
     </row>
     <row r="45" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B45" s="15">
         <v>31977</v>
@@ -14889,22 +14966,22 @@
       <c r="L45" s="45"/>
       <c r="M45" s="41"/>
       <c r="N45" s="116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O45" s="116"/>
       <c r="P45" s="116"/>
-      <c r="Q45" s="125">
+      <c r="Q45" s="129">
         <f>Q40-G12-G13</f>
         <v>235351.11712424085</v>
       </c>
-      <c r="R45" s="125"/>
-      <c r="S45" s="125"/>
+      <c r="R45" s="129"/>
+      <c r="S45" s="129"/>
       <c r="T45" s="41"/>
       <c r="U45" s="41"/>
     </row>
     <row r="46" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B46" s="15">
         <v>-55663</v>
@@ -14935,12 +15012,12 @@
       <c r="N46" s="116"/>
       <c r="O46" s="116"/>
       <c r="P46" s="116"/>
-      <c r="Q46" s="125"/>
-      <c r="R46" s="125"/>
-      <c r="S46" s="125"/>
+      <c r="Q46" s="129"/>
+      <c r="R46" s="129"/>
+      <c r="S46" s="129"/>
       <c r="T46" s="41"/>
       <c r="U46" s="116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V46" s="116"/>
       <c r="W46" s="116"/>
@@ -14948,7 +15025,7 @@
     </row>
     <row r="47" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B47" s="15">
         <v>-23686</v>
@@ -14979,20 +15056,20 @@
       <c r="N47" s="116"/>
       <c r="O47" s="116"/>
       <c r="P47" s="116"/>
-      <c r="Q47" s="125"/>
-      <c r="R47" s="125"/>
-      <c r="S47" s="125"/>
+      <c r="Q47" s="129"/>
+      <c r="R47" s="129"/>
+      <c r="S47" s="129"/>
       <c r="T47" s="41"/>
       <c r="U47" s="116"/>
       <c r="V47" s="116"/>
       <c r="W47" s="116"/>
       <c r="X47" s="116"/>
-      <c r="Z47" s="114">
+      <c r="Z47" s="119">
         <f>L51*0.75+Q49*0.25</f>
         <v>173.213622833795</v>
       </c>
-      <c r="AA47" s="115"/>
-      <c r="AB47" s="115"/>
+      <c r="AA47" s="120"/>
+      <c r="AB47" s="120"/>
     </row>
     <row r="48" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
@@ -15026,14 +15103,14 @@
       </c>
       <c r="I48" s="45"/>
       <c r="J48" s="116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K48" s="116"/>
-      <c r="L48" s="121">
+      <c r="L48" s="125">
         <f>L43*E50</f>
         <v>271.38472253392496</v>
       </c>
-      <c r="M48" s="121"/>
+      <c r="M48" s="125"/>
       <c r="N48" s="41"/>
       <c r="O48" s="41"/>
       <c r="P48" s="41"/>
@@ -15045,13 +15122,13 @@
       <c r="V48" s="116"/>
       <c r="W48" s="116"/>
       <c r="X48" s="116"/>
-      <c r="Z48" s="115"/>
-      <c r="AA48" s="115"/>
-      <c r="AB48" s="115"/>
+      <c r="Z48" s="120"/>
+      <c r="AA48" s="120"/>
+      <c r="AB48" s="120"/>
     </row>
     <row r="49" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="49">
         <f>'Historical Financials'!$H$29</f>
@@ -15078,31 +15155,31 @@
       <c r="I49" s="45"/>
       <c r="J49" s="116"/>
       <c r="K49" s="116"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
+      <c r="L49" s="125"/>
+      <c r="M49" s="125"/>
       <c r="N49" s="116" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O49" s="116"/>
       <c r="P49" s="116"/>
-      <c r="Q49" s="121">
+      <c r="Q49" s="125">
         <f>Q45/G14</f>
         <v>82.11832418849994</v>
       </c>
-      <c r="R49" s="121"/>
-      <c r="S49" s="121"/>
+      <c r="R49" s="125"/>
+      <c r="S49" s="125"/>
       <c r="T49" s="41"/>
       <c r="U49" s="116"/>
       <c r="V49" s="116"/>
       <c r="W49" s="116"/>
       <c r="X49" s="116"/>
-      <c r="Z49" s="115"/>
-      <c r="AA49" s="115"/>
-      <c r="AB49" s="115"/>
+      <c r="Z49" s="120"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="120"/>
     </row>
     <row r="50" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50" s="45">
         <f>B44/B49</f>
@@ -15135,14 +15212,14 @@
       <c r="I50" s="45"/>
       <c r="J50" s="116"/>
       <c r="K50" s="116"/>
-      <c r="L50" s="121"/>
-      <c r="M50" s="121"/>
+      <c r="L50" s="125"/>
+      <c r="M50" s="125"/>
       <c r="N50" s="116"/>
       <c r="O50" s="116"/>
       <c r="P50" s="116"/>
-      <c r="Q50" s="121"/>
-      <c r="R50" s="121"/>
-      <c r="S50" s="121"/>
+      <c r="Q50" s="125"/>
+      <c r="R50" s="125"/>
+      <c r="S50" s="125"/>
       <c r="T50" s="41"/>
       <c r="U50" s="116"/>
       <c r="V50" s="116"/>
@@ -15152,20 +15229,20 @@
     <row r="51" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I51" s="45"/>
       <c r="J51" s="116" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K51" s="116"/>
-      <c r="L51" s="119">
+      <c r="L51" s="123">
         <f>L48/(1+B15)^3</f>
         <v>203.57872238222669</v>
       </c>
-      <c r="M51" s="120"/>
+      <c r="M51" s="124"/>
       <c r="N51" s="116"/>
       <c r="O51" s="116"/>
       <c r="P51" s="116"/>
-      <c r="Q51" s="121"/>
-      <c r="R51" s="121"/>
-      <c r="S51" s="121"/>
+      <c r="Q51" s="125"/>
+      <c r="R51" s="125"/>
+      <c r="S51" s="125"/>
       <c r="T51" s="41"/>
       <c r="U51" s="41"/>
     </row>
@@ -15173,22 +15250,22 @@
       <c r="I52" s="45"/>
       <c r="J52" s="116"/>
       <c r="K52" s="116"/>
-      <c r="L52" s="120"/>
-      <c r="M52" s="120"/>
+      <c r="L52" s="124"/>
+      <c r="M52" s="124"/>
       <c r="N52" s="116"/>
       <c r="O52" s="116"/>
       <c r="P52" s="116"/>
-      <c r="Q52" s="121"/>
-      <c r="R52" s="121"/>
-      <c r="S52" s="121"/>
+      <c r="Q52" s="125"/>
+      <c r="R52" s="125"/>
+      <c r="S52" s="125"/>
       <c r="T52" s="41"/>
       <c r="U52" s="41"/>
     </row>
     <row r="53" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J53" s="116"/>
       <c r="K53" s="116"/>
-      <c r="L53" s="120"/>
-      <c r="M53" s="120"/>
+      <c r="L53" s="124"/>
+      <c r="M53" s="124"/>
       <c r="Q53" s="77"/>
       <c r="R53" s="77"/>
       <c r="S53" s="77"/>
@@ -15197,7 +15274,7 @@
     </row>
     <row r="54" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="111" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
@@ -15220,50 +15297,50 @@
     <row r="55" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="35"/>
       <c r="B55" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="66" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D55" s="66" t="s">
+      <c r="E55" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="E55" s="67" t="s">
-        <v>122</v>
-      </c>
       <c r="F55" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="67" t="s">
+      <c r="H55" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="H55" s="67" t="s">
-        <v>133</v>
-      </c>
       <c r="I55" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J55" s="45"/>
       <c r="K55" s="41"/>
       <c r="L55" s="41"/>
       <c r="M55" s="41"/>
       <c r="N55" s="116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O55" s="116"/>
       <c r="P55" s="116"/>
-      <c r="Q55" s="126">
+      <c r="Q55" s="130">
         <f>NPV(B15,C62:H62)</f>
         <v>155189.89102934275</v>
       </c>
-      <c r="R55" s="125"/>
-      <c r="S55" s="125"/>
+      <c r="R55" s="129"/>
+      <c r="S55" s="129"/>
       <c r="T55" s="41"/>
       <c r="U55" s="41"/>
     </row>
     <row r="56" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B56" s="49">
         <v>67357</v>
@@ -15297,15 +15374,15 @@
       <c r="N56" s="116"/>
       <c r="O56" s="116"/>
       <c r="P56" s="116"/>
-      <c r="Q56" s="125"/>
-      <c r="R56" s="125"/>
-      <c r="S56" s="125"/>
+      <c r="Q56" s="129"/>
+      <c r="R56" s="129"/>
+      <c r="S56" s="129"/>
       <c r="T56" s="41"/>
       <c r="U56" s="41"/>
     </row>
     <row r="57" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B57" s="49">
         <v>20606</v>
@@ -15330,7 +15407,7 @@
       </c>
       <c r="I57" s="48"/>
       <c r="J57" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K57" s="64"/>
       <c r="L57" s="64">
@@ -15340,15 +15417,15 @@
       <c r="N57" s="116"/>
       <c r="O57" s="116"/>
       <c r="P57" s="116"/>
-      <c r="Q57" s="125"/>
-      <c r="R57" s="125"/>
-      <c r="S57" s="125"/>
+      <c r="Q57" s="129"/>
+      <c r="R57" s="129"/>
+      <c r="S57" s="129"/>
       <c r="T57" s="41"/>
       <c r="U57" s="41"/>
     </row>
     <row r="58" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B58" s="49">
         <v>17087</v>
@@ -15387,7 +15464,7 @@
     </row>
     <row r="59" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B59" s="49">
         <v>31977</v>
@@ -15426,7 +15503,7 @@
     </row>
     <row r="60" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B60" s="49">
         <v>-55663</v>
@@ -15455,22 +15532,22 @@
       <c r="L60" s="41"/>
       <c r="M60" s="41"/>
       <c r="N60" s="116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O60" s="116"/>
       <c r="P60" s="116"/>
-      <c r="Q60" s="125">
+      <c r="Q60" s="129">
         <f>Q55-G12-G13</f>
         <v>51983.891029342747</v>
       </c>
-      <c r="R60" s="125"/>
-      <c r="S60" s="125"/>
+      <c r="R60" s="129"/>
+      <c r="S60" s="129"/>
       <c r="T60" s="41"/>
       <c r="U60" s="41"/>
     </row>
     <row r="61" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="49">
         <v>-23686</v>
@@ -15495,23 +15572,23 @@
       </c>
       <c r="I61" s="48"/>
       <c r="J61" s="116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K61" s="116"/>
-      <c r="L61" s="121">
+      <c r="L61" s="125">
         <f>L57*E64</f>
         <v>172.20722152951797</v>
       </c>
-      <c r="M61" s="121"/>
+      <c r="M61" s="125"/>
       <c r="N61" s="116"/>
       <c r="O61" s="116"/>
       <c r="P61" s="116"/>
-      <c r="Q61" s="125"/>
-      <c r="R61" s="125"/>
-      <c r="S61" s="125"/>
+      <c r="Q61" s="129"/>
+      <c r="R61" s="129"/>
+      <c r="S61" s="129"/>
       <c r="T61" s="41"/>
       <c r="U61" s="116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V61" s="116"/>
       <c r="W61" s="116"/>
@@ -15550,29 +15627,29 @@
       <c r="I62" s="48"/>
       <c r="J62" s="116"/>
       <c r="K62" s="116"/>
-      <c r="L62" s="121"/>
-      <c r="M62" s="121"/>
+      <c r="L62" s="125"/>
+      <c r="M62" s="125"/>
       <c r="N62" s="116"/>
       <c r="O62" s="116"/>
       <c r="P62" s="116"/>
-      <c r="Q62" s="125"/>
-      <c r="R62" s="125"/>
-      <c r="S62" s="125"/>
+      <c r="Q62" s="129"/>
+      <c r="R62" s="129"/>
+      <c r="S62" s="129"/>
       <c r="T62" s="41"/>
       <c r="U62" s="116"/>
       <c r="V62" s="116"/>
       <c r="W62" s="116"/>
       <c r="X62" s="116"/>
-      <c r="Z62" s="112">
+      <c r="Z62" s="117">
         <f>L64*0.75+Q64*0.25</f>
         <v>101.42021792047309</v>
       </c>
-      <c r="AA62" s="113"/>
-      <c r="AB62" s="113"/>
+      <c r="AA62" s="118"/>
+      <c r="AB62" s="118"/>
     </row>
     <row r="63" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="49">
         <f>'Historical Financials'!$H$29</f>
@@ -15599,8 +15676,8 @@
       <c r="I63" s="48"/>
       <c r="J63" s="116"/>
       <c r="K63" s="116"/>
-      <c r="L63" s="121"/>
-      <c r="M63" s="121"/>
+      <c r="L63" s="125"/>
+      <c r="M63" s="125"/>
       <c r="N63" s="41"/>
       <c r="O63" s="41"/>
       <c r="P63" s="41"/>
@@ -15612,13 +15689,13 @@
       <c r="V63" s="116"/>
       <c r="W63" s="116"/>
       <c r="X63" s="116"/>
-      <c r="Z63" s="113"/>
-      <c r="AA63" s="113"/>
-      <c r="AB63" s="113"/>
+      <c r="Z63" s="118"/>
+      <c r="AA63" s="118"/>
+      <c r="AB63" s="118"/>
     </row>
     <row r="64" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B64" s="65">
         <f>B58/B63</f>
@@ -15650,33 +15727,33 @@
       </c>
       <c r="I64" s="65"/>
       <c r="J64" s="116" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K64" s="116"/>
-      <c r="L64" s="117">
+      <c r="L64" s="121">
         <f>L61/(1+B15)^3</f>
         <v>129.18091267864165</v>
       </c>
-      <c r="M64" s="118"/>
+      <c r="M64" s="122"/>
       <c r="N64" s="116" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O64" s="116"/>
       <c r="P64" s="116"/>
-      <c r="Q64" s="121">
+      <c r="Q64" s="125">
         <f>Q60/G14</f>
         <v>18.138133645967461</v>
       </c>
-      <c r="R64" s="121"/>
-      <c r="S64" s="121"/>
+      <c r="R64" s="125"/>
+      <c r="S64" s="125"/>
       <c r="T64" s="41"/>
       <c r="U64" s="116"/>
       <c r="V64" s="116"/>
       <c r="W64" s="116"/>
       <c r="X64" s="116"/>
-      <c r="Z64" s="113"/>
-      <c r="AA64" s="113"/>
-      <c r="AB64" s="113"/>
+      <c r="Z64" s="118"/>
+      <c r="AA64" s="118"/>
+      <c r="AB64" s="118"/>
     </row>
     <row r="65" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="25"/>
@@ -15690,14 +15767,14 @@
       <c r="I65" s="65"/>
       <c r="J65" s="116"/>
       <c r="K65" s="116"/>
-      <c r="L65" s="118"/>
-      <c r="M65" s="118"/>
+      <c r="L65" s="122"/>
+      <c r="M65" s="122"/>
       <c r="N65" s="116"/>
       <c r="O65" s="116"/>
       <c r="P65" s="116"/>
-      <c r="Q65" s="121"/>
-      <c r="R65" s="121"/>
-      <c r="S65" s="121"/>
+      <c r="Q65" s="125"/>
+      <c r="R65" s="125"/>
+      <c r="S65" s="125"/>
       <c r="T65" s="41"/>
       <c r="U65" s="116"/>
       <c r="V65" s="116"/>
@@ -15716,14 +15793,14 @@
       <c r="I66" s="65"/>
       <c r="J66" s="116"/>
       <c r="K66" s="116"/>
-      <c r="L66" s="118"/>
-      <c r="M66" s="118"/>
+      <c r="L66" s="122"/>
+      <c r="M66" s="122"/>
       <c r="N66" s="116"/>
       <c r="O66" s="116"/>
       <c r="P66" s="116"/>
-      <c r="Q66" s="121"/>
-      <c r="R66" s="121"/>
-      <c r="S66" s="121"/>
+      <c r="Q66" s="125"/>
+      <c r="R66" s="125"/>
+      <c r="S66" s="125"/>
       <c r="T66" s="41"/>
       <c r="U66" s="41"/>
     </row>
@@ -15744,9 +15821,9 @@
       <c r="N67" s="116"/>
       <c r="O67" s="116"/>
       <c r="P67" s="116"/>
-      <c r="Q67" s="121"/>
-      <c r="R67" s="121"/>
-      <c r="S67" s="121"/>
+      <c r="Q67" s="125"/>
+      <c r="R67" s="125"/>
+      <c r="S67" s="125"/>
       <c r="T67" s="41"/>
       <c r="U67" s="41"/>
     </row>
@@ -16011,62 +16088,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="132" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
+      <c r="A1" s="131" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3" s="95" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C3" s="95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D3" s="95" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" s="95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F3" s="95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G3" s="95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H3" s="95" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I3" s="95" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J3" s="95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K3" s="95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L3" s="95" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="100">
         <v>22</v>
@@ -16114,7 +16191,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="100">
         <v>18</v>
@@ -16162,7 +16239,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="100">
         <v>15</v>
@@ -16209,48 +16286,48 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="133" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="F9" s="133" t="s">
+      <c r="A9" s="132" t="s">
         <v>204</v>
       </c>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="F9" s="132" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B10" s="95" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" s="95" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F10" s="95" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G10" s="95" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H10" s="95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I10" s="95" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B11" s="93">
         <f>L4</f>
@@ -16265,7 +16342,7 @@
         <v>363.4794640963849</v>
       </c>
       <c r="F11" s="82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G11" s="93">
         <f>L6</f>
@@ -16282,7 +16359,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" s="93">
         <f>L5</f>
@@ -16297,7 +16374,7 @@
         <v>222.27268298526448</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G12" s="93">
         <f>D13</f>
@@ -16314,7 +16391,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" s="93">
         <f>L6</f>
@@ -16330,20 +16407,20 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="134" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="134"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
+      <c r="A16" s="133" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -16365,71 +16442,71 @@
   </cols>
   <sheetData>
     <row r="18" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="135" t="s">
-        <v>220</v>
-      </c>
-      <c r="B18" s="136"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="136"/>
+      <c r="A18" s="134" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="135"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
     </row>
     <row r="19" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="136"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="136"/>
+      <c r="A19" s="135"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
     </row>
     <row r="20" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="136"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
+      <c r="A20" s="135"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
     </row>
     <row r="21" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="136"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="136"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="136"/>
+      <c r="A21" s="135"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
     </row>
     <row r="22" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="136"/>
-      <c r="B22" s="136"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
     </row>
     <row r="23" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="102" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B23" s="103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C23" s="102" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B24" s="104">
         <f>DCF!Z62</f>
@@ -16446,7 +16523,7 @@
     </row>
     <row r="25" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" s="104">
         <f>'EV EBITDA '!G12</f>
@@ -16463,7 +16540,7 @@
     </row>
     <row r="26" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="102" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B26" s="104">
         <f>Comps!E22</f>
@@ -16506,21 +16583,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1" s="108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C1" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2">
         <v>22.8</v>
@@ -16528,10 +16605,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C3">
         <v>31</v>
@@ -16539,10 +16616,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="107" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4">
         <v>33</v>
@@ -16550,10 +16627,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -16561,10 +16638,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="107" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6">
         <v>52</v>
@@ -16572,10 +16649,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="107" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -16583,7 +16660,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="107" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B9" s="106"/>
       <c r="C9">
@@ -16593,18 +16670,18 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C12" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="107" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="107" t="s">
+      <c r="E12" s="107" t="s">
         <v>158</v>
-      </c>
-      <c r="E12" s="107" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="107" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" s="106"/>
       <c r="C13" s="41">
@@ -16622,7 +16699,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" s="106"/>
       <c r="C14" s="41">
@@ -16640,7 +16717,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="107" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" s="106"/>
       <c r="C15" s="91">
@@ -16658,7 +16735,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="107" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B16" s="106"/>
       <c r="C16" s="91">
@@ -16676,7 +16753,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="107" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B19" s="92">
         <v>0.25</v>
@@ -16684,7 +16761,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B20" s="92">
         <v>0.75</v>
@@ -16692,7 +16769,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22" s="107"/>
       <c r="C22" s="91">
@@ -16728,7 +16805,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" x14ac:dyDescent="0.2">
       <c r="A1" s="80" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B1" s="81"/>
       <c r="C1" s="81"/>
@@ -16740,7 +16817,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="83" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -16761,26 +16838,26 @@
       <c r="H3" s="81"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="137" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
+      <c r="A4" s="136" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="136"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
       <c r="E4" s="81"/>
       <c r="F4" s="84" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="H4" s="84" t="s">
         <v>167</v>
-      </c>
-      <c r="H4" s="84" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="86">
         <v>0.03</v>
@@ -16793,7 +16870,7 @@
       </c>
       <c r="E5" s="81"/>
       <c r="F5" s="87" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G5" s="88">
         <f>D8</f>
@@ -16823,7 +16900,7 @@
       </c>
       <c r="E6" s="81"/>
       <c r="F6" s="87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G6" s="88">
         <f>C18</f>
@@ -16853,7 +16930,7 @@
       </c>
       <c r="E7" s="81"/>
       <c r="F7" s="87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G7" s="88">
         <f>B28</f>
@@ -16961,12 +17038,12 @@
       <c r="H13" s="81"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="137" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="137"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
+      <c r="A14" s="136" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
       <c r="E14" s="81"/>
       <c r="F14" s="81"/>
       <c r="G14" s="81"/>
@@ -16974,7 +17051,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="86">
         <v>0.03</v>
@@ -17131,12 +17208,12 @@
       <c r="H23" s="81"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="137" t="s">
-        <v>174</v>
-      </c>
-      <c r="B24" s="137"/>
-      <c r="C24" s="137"/>
-      <c r="D24" s="137"/>
+      <c r="A24" s="136" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="136"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="136"/>
       <c r="E24" s="81"/>
       <c r="F24" s="81"/>
       <c r="G24" s="81"/>
@@ -17144,7 +17221,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="86">
         <v>0.03</v>
